--- a/artfynd/A 67351-2020 artfynd.xlsx
+++ b/artfynd/A 67351-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123429171</v>
+        <v>123429349</v>
       </c>
       <c r="B2" t="n">
-        <v>5173</v>
+        <v>8430</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388471</v>
+        <v>388441</v>
       </c>
       <c r="R2" t="n">
-        <v>6585574</v>
+        <v>6585597</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -895,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123429349</v>
+        <v>123429343</v>
       </c>
       <c r="B4" t="n">
         <v>8430</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388441</v>
+        <v>388489</v>
       </c>
       <c r="R4" t="n">
-        <v>6585597</v>
+        <v>6585562</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123429343</v>
+        <v>123429171</v>
       </c>
       <c r="B5" t="n">
-        <v>8430</v>
+        <v>5173</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,21 +1021,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388489</v>
+        <v>388471</v>
       </c>
       <c r="R5" t="n">
-        <v>6585562</v>
+        <v>6585574</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 67351-2020 artfynd.xlsx
+++ b/artfynd/A 67351-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123429349</v>
+        <v>123429170</v>
       </c>
       <c r="B2" t="n">
-        <v>8430</v>
+        <v>5174</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388441</v>
+        <v>388501</v>
       </c>
       <c r="R2" t="n">
-        <v>6585597</v>
+        <v>6585567</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123429170</v>
+        <v>123429171</v>
       </c>
       <c r="B3" t="n">
-        <v>5173</v>
+        <v>5174</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388501</v>
+        <v>388471</v>
       </c>
       <c r="R3" t="n">
-        <v>6585567</v>
+        <v>6585574</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123429171</v>
+        <v>123429343</v>
       </c>
       <c r="B4" t="n">
-        <v>5173</v>
+        <v>8434</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388471</v>
+        <v>388489</v>
       </c>
       <c r="R4" t="n">
-        <v>6585574</v>
+        <v>6585562</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123429343</v>
+        <v>123429349</v>
       </c>
       <c r="B5" t="n">
-        <v>8430</v>
+        <v>8434</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388489</v>
+        <v>388441</v>
       </c>
       <c r="R5" t="n">
-        <v>6585562</v>
+        <v>6585597</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 67351-2020 artfynd.xlsx
+++ b/artfynd/A 67351-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123429170</v>
+        <v>123429349</v>
       </c>
       <c r="B2" t="n">
-        <v>5174</v>
+        <v>8436</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388501</v>
+        <v>388441</v>
       </c>
       <c r="R2" t="n">
-        <v>6585567</v>
+        <v>6585597</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -788,7 +788,7 @@
         <v>123429171</v>
       </c>
       <c r="B3" t="n">
-        <v>5174</v>
+        <v>5176</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123429343</v>
+        <v>123429170</v>
       </c>
       <c r="B4" t="n">
-        <v>8434</v>
+        <v>5176</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388489</v>
+        <v>388501</v>
       </c>
       <c r="R4" t="n">
-        <v>6585562</v>
+        <v>6585567</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123429349</v>
+        <v>123429343</v>
       </c>
       <c r="B5" t="n">
-        <v>8434</v>
+        <v>8436</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388441</v>
+        <v>388489</v>
       </c>
       <c r="R5" t="n">
-        <v>6585597</v>
+        <v>6585562</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 67351-2020 artfynd.xlsx
+++ b/artfynd/A 67351-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123429349</v>
+        <v>123429170</v>
       </c>
       <c r="B2" t="n">
-        <v>8436</v>
+        <v>5176</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388441</v>
+        <v>388501</v>
       </c>
       <c r="R2" t="n">
-        <v>6585597</v>
+        <v>6585567</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123429170</v>
+        <v>123429343</v>
       </c>
       <c r="B4" t="n">
-        <v>5176</v>
+        <v>8436</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388501</v>
+        <v>388489</v>
       </c>
       <c r="R4" t="n">
-        <v>6585567</v>
+        <v>6585562</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1005,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123429343</v>
+        <v>123429349</v>
       </c>
       <c r="B5" t="n">
         <v>8436</v>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388489</v>
+        <v>388441</v>
       </c>
       <c r="R5" t="n">
-        <v>6585562</v>
+        <v>6585597</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 67351-2020 artfynd.xlsx
+++ b/artfynd/A 67351-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123429170</v>
+        <v>123429343</v>
       </c>
       <c r="B2" t="n">
-        <v>5176</v>
+        <v>8436</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388501</v>
+        <v>388489</v>
       </c>
       <c r="R2" t="n">
-        <v>6585567</v>
+        <v>6585562</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123429171</v>
+        <v>123429170</v>
       </c>
       <c r="B3" t="n">
         <v>5176</v>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388471</v>
+        <v>388501</v>
       </c>
       <c r="R3" t="n">
-        <v>6585574</v>
+        <v>6585567</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123429343</v>
+        <v>123429171</v>
       </c>
       <c r="B4" t="n">
-        <v>8436</v>
+        <v>5176</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388489</v>
+        <v>388471</v>
       </c>
       <c r="R4" t="n">
-        <v>6585562</v>
+        <v>6585574</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 67351-2020 artfynd.xlsx
+++ b/artfynd/A 67351-2020 artfynd.xlsx
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123429170</v>
+        <v>123429171</v>
       </c>
       <c r="B3" t="n">
         <v>5176</v>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388501</v>
+        <v>388471</v>
       </c>
       <c r="R3" t="n">
-        <v>6585567</v>
+        <v>6585574</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123429171</v>
+        <v>123429349</v>
       </c>
       <c r="B4" t="n">
-        <v>5176</v>
+        <v>8436</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388471</v>
+        <v>388441</v>
       </c>
       <c r="R4" t="n">
-        <v>6585574</v>
+        <v>6585597</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123429349</v>
+        <v>123429170</v>
       </c>
       <c r="B5" t="n">
-        <v>8436</v>
+        <v>5176</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,21 +1021,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388441</v>
+        <v>388501</v>
       </c>
       <c r="R5" t="n">
-        <v>6585597</v>
+        <v>6585567</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 67351-2020 artfynd.xlsx
+++ b/artfynd/A 67351-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123429343</v>
+        <v>123429170</v>
       </c>
       <c r="B2" t="n">
-        <v>8436</v>
+        <v>5176</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388489</v>
+        <v>388501</v>
       </c>
       <c r="R2" t="n">
-        <v>6585562</v>
+        <v>6585567</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123429171</v>
+        <v>123429349</v>
       </c>
       <c r="B3" t="n">
-        <v>5176</v>
+        <v>8436</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388471</v>
+        <v>388441</v>
       </c>
       <c r="R3" t="n">
-        <v>6585574</v>
+        <v>6585597</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123429349</v>
+        <v>123429343</v>
       </c>
       <c r="B4" t="n">
         <v>8436</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388441</v>
+        <v>388489</v>
       </c>
       <c r="R4" t="n">
-        <v>6585597</v>
+        <v>6585562</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1005,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123429170</v>
+        <v>123429171</v>
       </c>
       <c r="B5" t="n">
         <v>5176</v>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388501</v>
+        <v>388471</v>
       </c>
       <c r="R5" t="n">
-        <v>6585567</v>
+        <v>6585574</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 67351-2020 artfynd.xlsx
+++ b/artfynd/A 67351-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123429170</v>
+        <v>123429349</v>
       </c>
       <c r="B2" t="n">
-        <v>5176</v>
+        <v>8436</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388501</v>
+        <v>388441</v>
       </c>
       <c r="R2" t="n">
-        <v>6585567</v>
+        <v>6585597</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123429349</v>
+        <v>123429343</v>
       </c>
       <c r="B3" t="n">
         <v>8436</v>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388441</v>
+        <v>388489</v>
       </c>
       <c r="R3" t="n">
-        <v>6585597</v>
+        <v>6585562</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123429343</v>
+        <v>123429170</v>
       </c>
       <c r="B4" t="n">
-        <v>8436</v>
+        <v>5176</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388489</v>
+        <v>388501</v>
       </c>
       <c r="R4" t="n">
-        <v>6585562</v>
+        <v>6585567</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 67351-2020 artfynd.xlsx
+++ b/artfynd/A 67351-2020 artfynd.xlsx
@@ -895,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123429170</v>
+        <v>123429171</v>
       </c>
       <c r="B4" t="n">
         <v>5176</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388501</v>
+        <v>388471</v>
       </c>
       <c r="R4" t="n">
-        <v>6585567</v>
+        <v>6585574</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1005,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123429171</v>
+        <v>123429170</v>
       </c>
       <c r="B5" t="n">
         <v>5176</v>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388471</v>
+        <v>388501</v>
       </c>
       <c r="R5" t="n">
-        <v>6585574</v>
+        <v>6585567</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
